--- a/output/2025_A24_SECCION_E_TABLAS.xlsx
+++ b/output/2025_A24_SECCION_E_TABLAS.xlsx
@@ -78,7 +78,7 @@
     <t>Servicio de Salud Metropolitano Sur</t>
   </si>
   <si>
-    <t>Servicio de Salud Metropolitano Sur Oriente</t>
+    <t>Servicio de Salud Metropolitano Sur - Oriente</t>
   </si>
   <si>
     <t>nombre_comuna</t>
